--- a/Result/profitability/4952.xlsx
+++ b/Result/profitability/4952.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38125</v>
+        <v>0.45875</v>
       </c>
       <c r="N2" t="n">
-        <v>34.3925</v>
+        <v>34.68875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,16 +681,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5725</v>
+        <v>0.71375</v>
       </c>
       <c r="N3" t="n">
-        <v>34.44</v>
+        <v>35.51</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5912500000000001</v>
+        <v>0.68625</v>
       </c>
       <c r="N4" t="n">
-        <v>34.51875</v>
+        <v>34.885</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7662500000000001</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>34.17</v>
+        <v>34.58125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.87125</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>33.97499999999999</v>
+        <v>35.15</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.88</v>
+        <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>34.3775</v>
+        <v>35.69125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4952</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>833</v>
+      </c>
+      <c r="D69" t="n">
+        <v>503</v>
+      </c>
+      <c r="E69" t="n">
+        <v>329</v>
+      </c>
+      <c r="F69" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="G69" t="n">
+        <v>132</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>15.90%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>9</v>
+      </c>
+      <c r="J69" t="n">
+        <v>141</v>
+      </c>
+      <c r="K69" t="n">
+        <v>129</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="N69" t="n">
+        <v>34.59125</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.530000000000001</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.06835990272899228</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.313725490196078</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>3.289999999999999</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.09075862068965512</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
